--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_16_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_16_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37E3BBC-7B19-448D-9076-2D0047380D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE515BC-BA79-4435-A3ED-6C5FCC9F5EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,70 +55,94 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT DLF 31 Jul 2025 800 PE</t>
-  </si>
-  <si>
-    <t>28-07-2025</t>
-  </si>
-  <si>
-    <t>OPT LODHA 31 Jul 2025 1220 PE</t>
-  </si>
-  <si>
-    <t>OPT LAURUSLABS 31 Jul 2025 880 CE</t>
-  </si>
-  <si>
-    <t>OPT LAURUSLABS 31 Jul 2025 890 PE</t>
-  </si>
-  <si>
-    <t>OPT PETRONET 31 Jul 2025 300 PE</t>
-  </si>
-  <si>
-    <t>29-07-2025</t>
-  </si>
-  <si>
-    <t>OPT TORNTPHARM 31 Jul 2025 3700 CE</t>
-  </si>
-  <si>
-    <t>OPT JSWSTEEL 31 Jul 2025 1050 CE</t>
-  </si>
-  <si>
-    <t>OPT VBL 31 Jul 2025 530 CE</t>
-  </si>
-  <si>
-    <t>30-07-2025</t>
-  </si>
-  <si>
-    <t>OPT POONAWALLA 31 Jul 2025 430 CE</t>
-  </si>
-  <si>
-    <t>OPT BOSCHLTD 31 Jul 2025 39500 PE</t>
-  </si>
-  <si>
-    <t>OPT HINDUNILVR 28 Aug 2025 2500 CE</t>
-  </si>
-  <si>
-    <t>31-07-2025</t>
-  </si>
-  <si>
-    <t>OPT ZYDUSLIFE 28 Aug 2025 980 PE</t>
-  </si>
-  <si>
-    <t>OPT KAYNES 28 Aug 2025 6100 PE</t>
-  </si>
-  <si>
-    <t>OPT KAYNES 28 Aug 2025 6000 CE</t>
-  </si>
-  <si>
-    <t>OPT HINDUNILVR 28 Aug 2025 2560 PE</t>
-  </si>
-  <si>
-    <t>01-08-2025</t>
-  </si>
-  <si>
-    <t>OPT HINDUNILVR 28 Aug 2025 2560 CE</t>
-  </si>
-  <si>
-    <t>OPT DIVISLAB 28 Aug 2025 6400 PE</t>
+    <t>FUT TCS 30 Sep 2025</t>
+  </si>
+  <si>
+    <t>01-09-2025</t>
+  </si>
+  <si>
+    <t>OPT TCS 30 Sep 2025 2900 PE</t>
+  </si>
+  <si>
+    <t>OPT ASIANPAINT 30 Sep 2025 2500 CE</t>
+  </si>
+  <si>
+    <t>OPT MUTHOOTFIN 30 Sep 2025 2700 CE</t>
+  </si>
+  <si>
+    <t>02-09-2025</t>
+  </si>
+  <si>
+    <t>OPT DABUR 30 Sep 2025 530 CE</t>
+  </si>
+  <si>
+    <t>OPT EICHERMOT 30 Sep 2025 6300 CE</t>
+  </si>
+  <si>
+    <t>OPT RELIANCE 30 Sep 2025 1380 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 02 Sep 2025 24500 PE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 02 Sep 2025 24700 PE</t>
+  </si>
+  <si>
+    <t>OPT TATAMOTORS 30 Sep 2025 680 CE</t>
+  </si>
+  <si>
+    <t>OPT HEROMOTOCO 30 Sep 2025 5300 CE</t>
+  </si>
+  <si>
+    <t>OPT DELHIVERY 30 Sep 2025 480 CE</t>
+  </si>
+  <si>
+    <t>03-09-2025</t>
+  </si>
+  <si>
+    <t>OPT MANAPPURAM 30 Sep 2025 290 CE</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 30 Sep 2025 1060 CE</t>
+  </si>
+  <si>
+    <t>OPT HINDALCO 30 Sep 2025 720 CE</t>
+  </si>
+  <si>
+    <t>OPT GODREJCP 30 Sep 2025 1260 PE</t>
+  </si>
+  <si>
+    <t>04-09-2025</t>
+  </si>
+  <si>
+    <t>OPT BAJFINANCE 30 Sep 2025 940 PE</t>
+  </si>
+  <si>
+    <t>OPT GODREJCP 30 Sep 2025 1280 PE</t>
+  </si>
+  <si>
+    <t>OPT BAJAJFINSV 30 Sep 2025 2000 CE</t>
+  </si>
+  <si>
+    <t>OPT ICICIGI 30 Sep 2025 1860 CE</t>
+  </si>
+  <si>
+    <t>OPT LTIM 30 Sep 2025 5100 PE</t>
+  </si>
+  <si>
+    <t>05-09-2025</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 09 Sep 2025 24700 PE</t>
+  </si>
+  <si>
+    <t>OPT LTIM 30 Sep 2025 5200 PE</t>
+  </si>
+  <si>
+    <t>OPT M&amp;M 30 Sep 2025 3500 CE</t>
+  </si>
+  <si>
+    <t>OPT EICHERMOT 30 Sep 2025 6500 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -471,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -490,10 +514,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -502,10 +526,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -528,801 +552,1177 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45866</v>
+        <v>45901</v>
       </c>
       <c r="D2">
-        <v>1650</v>
+        <v>175</v>
       </c>
       <c r="E2">
-        <v>10.15</v>
+        <v>3139.8</v>
       </c>
       <c r="F2">
-        <v>16747.5</v>
+        <v>549465</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>1650</v>
+        <v>175</v>
       </c>
       <c r="I2">
-        <v>11.55</v>
+        <v>3130.1</v>
       </c>
       <c r="J2">
-        <v>19057.5</v>
+        <v>547767.5</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>2310</v>
+        <v>-1697.5</v>
       </c>
       <c r="M2">
-        <v>105.41</v>
+        <v>193.31</v>
       </c>
       <c r="N2">
-        <v>2204.59</v>
+        <v>-1890.81</v>
       </c>
       <c r="O2">
-        <v>2310</v>
+        <v>1697.5</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45866</v>
+        <v>45901</v>
       </c>
       <c r="D3">
-        <v>450</v>
+        <v>175</v>
       </c>
       <c r="E3">
-        <v>19.7</v>
+        <v>6.85</v>
       </c>
       <c r="F3">
-        <v>8865</v>
+        <v>1198.75</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>450</v>
+        <v>175</v>
       </c>
       <c r="I3">
-        <v>12.5</v>
+        <v>6.65</v>
       </c>
       <c r="J3">
-        <v>5625</v>
+        <v>1163.75</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-3240</v>
+        <v>-35</v>
       </c>
       <c r="M3">
-        <v>59.19</v>
+        <v>49.39</v>
       </c>
       <c r="N3">
-        <v>-3299.19</v>
+        <v>-84.39</v>
       </c>
       <c r="O3">
-        <v>3240</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45866</v>
+        <v>45901</v>
       </c>
       <c r="D4">
-        <v>1700</v>
+        <v>250</v>
       </c>
       <c r="E4">
-        <v>19.100000000000001</v>
+        <v>90</v>
       </c>
       <c r="F4">
-        <v>32470</v>
+        <v>22500</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H4">
-        <v>1700</v>
+        <v>250</v>
       </c>
       <c r="I4">
-        <v>23.1</v>
+        <v>84</v>
       </c>
       <c r="J4">
-        <v>39270</v>
+        <v>21000</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>6800</v>
+        <v>-1500</v>
       </c>
       <c r="M4">
-        <v>117.98</v>
+        <v>87.17</v>
       </c>
       <c r="N4">
-        <v>6682.02</v>
+        <v>-1587.17</v>
       </c>
       <c r="O4">
-        <v>6800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>45866</v>
+        <v>45902</v>
       </c>
       <c r="D5">
-        <v>1700</v>
+        <v>275</v>
       </c>
       <c r="E5">
-        <v>15.75</v>
+        <v>117.2</v>
       </c>
       <c r="F5">
-        <v>26775</v>
+        <v>32230</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>1700</v>
+        <v>275</v>
       </c>
       <c r="I5">
-        <v>13.6</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>23120</v>
+        <v>30250</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-3655</v>
+        <v>-1980</v>
       </c>
       <c r="M5">
-        <v>92.1</v>
+        <v>104.69</v>
       </c>
       <c r="N5">
-        <v>-3747.1</v>
+        <v>-2084.69</v>
       </c>
       <c r="O5">
-        <v>3655</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>229</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45902</v>
+      </c>
+      <c r="D6">
+        <v>2500</v>
+      </c>
+      <c r="E6">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="F6">
+        <v>48500</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1">
-        <v>45867</v>
-      </c>
-      <c r="D6">
-        <v>5400</v>
-      </c>
-      <c r="E6">
-        <v>7.17</v>
-      </c>
-      <c r="F6">
-        <v>38700</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="H6">
-        <v>5400</v>
+        <v>2500</v>
       </c>
       <c r="I6">
-        <v>6.77</v>
+        <v>21.6</v>
       </c>
       <c r="J6">
-        <v>36540</v>
+        <v>54000</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-2160</v>
+        <v>5500</v>
       </c>
       <c r="M6">
-        <v>210.93</v>
+        <v>145.13999999999999</v>
       </c>
       <c r="N6">
-        <v>-2370.9299999999998</v>
+        <v>5354.86</v>
       </c>
       <c r="O6">
-        <v>2160</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>281</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>45867</v>
+        <v>45902</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="E7">
-        <v>79.2</v>
+        <v>163</v>
       </c>
       <c r="F7">
-        <v>19800</v>
+        <v>28525</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="I7">
-        <v>76</v>
+        <v>167.75</v>
       </c>
       <c r="J7">
-        <v>19000</v>
+        <v>29356.25</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>-800</v>
+        <v>831.25</v>
       </c>
       <c r="M7">
-        <v>82.97</v>
+        <v>101.76</v>
       </c>
       <c r="N7">
-        <v>-882.97</v>
+        <v>729.49</v>
       </c>
       <c r="O7">
-        <v>800</v>
+        <v>831.25</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45867</v>
+        <v>45902</v>
       </c>
       <c r="D8">
-        <v>675</v>
+        <v>500</v>
       </c>
       <c r="E8">
-        <v>11.1</v>
+        <v>31.15</v>
       </c>
       <c r="F8">
-        <v>7492.5</v>
+        <v>15575</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>675</v>
+        <v>500</v>
       </c>
       <c r="I8">
-        <v>9.8000000000000007</v>
+        <v>30.1</v>
       </c>
       <c r="J8">
-        <v>6615</v>
+        <v>15050</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>-877.5</v>
+        <v>-525</v>
       </c>
       <c r="M8">
-        <v>59.97</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="N8">
-        <v>-937.47</v>
+        <v>-600.6</v>
       </c>
       <c r="O8">
-        <v>877.5</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>286</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>45868</v>
+        <v>45902</v>
       </c>
       <c r="D9">
-        <v>1025</v>
+        <v>300</v>
       </c>
       <c r="E9">
-        <v>3.35</v>
+        <v>13.18</v>
       </c>
       <c r="F9">
-        <v>3433.75</v>
+        <v>3952.5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H9">
-        <v>1025</v>
+        <v>300</v>
       </c>
       <c r="I9">
-        <v>1.95</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J9">
-        <v>1998.75</v>
+        <v>2610</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>-1435</v>
+        <v>-1342.5</v>
       </c>
       <c r="M9">
-        <v>51.58</v>
+        <v>99.89</v>
       </c>
       <c r="N9">
-        <v>-1486.58</v>
+        <v>-1442.39</v>
       </c>
       <c r="O9">
-        <v>1435</v>
+        <v>1342.5</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>45868</v>
+        <v>45902</v>
       </c>
       <c r="D10">
-        <v>1700</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>2.2999999999999998</v>
+        <v>18.8</v>
       </c>
       <c r="F10">
-        <v>3910</v>
+        <v>2820</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H10">
-        <v>1700</v>
+        <v>150</v>
       </c>
       <c r="I10">
-        <v>1.5</v>
+        <v>10.75</v>
       </c>
       <c r="J10">
-        <v>2550</v>
+        <v>1612.5</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>-1360</v>
+        <v>-1207.5</v>
       </c>
       <c r="M10">
-        <v>52.59</v>
+        <v>50.75</v>
       </c>
       <c r="N10">
-        <v>-1412.59</v>
+        <v>-1258.25</v>
       </c>
       <c r="O10">
-        <v>1360</v>
+        <v>1207.5</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>49</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>45868</v>
+        <v>45902</v>
       </c>
       <c r="D11">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="E11">
-        <v>159.33000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="F11">
-        <v>11950</v>
+        <v>22480</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H11">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="I11">
-        <v>145</v>
+        <v>29.1</v>
       </c>
       <c r="J11">
-        <v>10875</v>
+        <v>23280</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>-1075</v>
+        <v>800</v>
       </c>
       <c r="M11">
-        <v>91.61</v>
+        <v>90.39</v>
       </c>
       <c r="N11">
-        <v>-1166.6099999999999</v>
+        <v>709.61</v>
       </c>
       <c r="O11">
-        <v>1075</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>45869</v>
+        <v>45902</v>
       </c>
       <c r="D12">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E12">
-        <v>75.099999999999994</v>
+        <v>150.69999999999999</v>
       </c>
       <c r="F12">
-        <v>22530</v>
+        <v>22605</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H12">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I12">
-        <v>85</v>
+        <v>107.7</v>
       </c>
       <c r="J12">
-        <v>25500</v>
+        <v>16155</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>2970</v>
+        <v>-6450</v>
       </c>
       <c r="M12">
-        <v>93.57</v>
+        <v>80.34</v>
       </c>
       <c r="N12">
-        <v>2876.43</v>
+        <v>-6530.34</v>
       </c>
       <c r="O12">
-        <v>2970</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>290</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1">
-        <v>45869</v>
+        <v>45903</v>
       </c>
       <c r="D13">
-        <v>1800</v>
+        <v>2075</v>
       </c>
       <c r="E13">
-        <v>35.479999999999997</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="F13">
-        <v>63855</v>
+        <v>36001.25</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H13">
-        <v>1800</v>
+        <v>2075</v>
       </c>
       <c r="I13">
-        <v>31.63</v>
+        <v>18</v>
       </c>
       <c r="J13">
-        <v>56925</v>
+        <v>37350</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>-6930</v>
+        <v>1348.75</v>
       </c>
       <c r="M13">
-        <v>180.43</v>
+        <v>116.74</v>
       </c>
       <c r="N13">
-        <v>-7110.43</v>
+        <v>1232.01</v>
       </c>
       <c r="O13">
-        <v>6930</v>
+        <v>1348.75</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
-        <v>45869</v>
+        <v>45903</v>
       </c>
       <c r="D14">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="E14">
-        <v>206.8</v>
+        <v>10.73</v>
       </c>
       <c r="F14">
-        <v>206800</v>
+        <v>64350</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H14">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I14">
-        <v>210.6</v>
+        <v>10.5</v>
       </c>
       <c r="J14">
-        <v>210599.98</v>
+        <v>63000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>3799.98</v>
+        <v>-1350</v>
       </c>
       <c r="M14">
-        <v>534.12</v>
+        <v>212.87</v>
       </c>
       <c r="N14">
-        <v>3265.86</v>
+        <v>-1562.87</v>
       </c>
       <c r="O14">
-        <v>3799.98</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
-        <v>45869</v>
+        <v>45903</v>
       </c>
       <c r="D15">
-        <v>200</v>
+        <v>675</v>
       </c>
       <c r="E15">
-        <v>323.55</v>
+        <v>28.55</v>
       </c>
       <c r="F15">
-        <v>64710</v>
+        <v>19271.25</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H15">
-        <v>200</v>
+        <v>675</v>
       </c>
       <c r="I15">
-        <v>330</v>
+        <v>30.6</v>
       </c>
       <c r="J15">
-        <v>66000</v>
+        <v>20655</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1290</v>
+        <v>1383.75</v>
       </c>
       <c r="M15">
-        <v>170.1</v>
+        <v>85.23</v>
       </c>
       <c r="N15">
-        <v>1119.9000000000001</v>
+        <v>1298.52</v>
       </c>
       <c r="O15">
-        <v>1290</v>
+        <v>1383.75</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1">
-        <v>45870</v>
+        <v>45903</v>
       </c>
       <c r="D16">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="E16">
-        <v>48</v>
+        <v>23.65</v>
       </c>
       <c r="F16">
-        <v>14400</v>
+        <v>33110</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H16">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="I16">
-        <v>45.15</v>
+        <v>25.1</v>
       </c>
       <c r="J16">
-        <v>13545</v>
+        <v>35140</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>-855</v>
+        <v>2030</v>
       </c>
       <c r="M16">
-        <v>72.930000000000007</v>
+        <v>112.02</v>
       </c>
       <c r="N16">
-        <v>-927.93</v>
+        <v>1917.98</v>
       </c>
       <c r="O16">
-        <v>855</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1">
-        <v>45870</v>
+        <v>45904</v>
       </c>
       <c r="D17">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E17">
-        <v>63.65</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="F17">
-        <v>19095</v>
+        <v>16975</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H17">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I17">
-        <v>60.55</v>
+        <v>34</v>
       </c>
       <c r="J17">
-        <v>18165</v>
+        <v>17000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>-930</v>
+        <v>25</v>
       </c>
       <c r="M17">
-        <v>82.29</v>
+        <v>78.989999999999995</v>
       </c>
       <c r="N17">
-        <v>-1012.29</v>
+        <v>-53.99</v>
       </c>
       <c r="O17">
-        <v>930</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1">
-        <v>45870</v>
+        <v>45904</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="E18">
-        <v>174.85</v>
+        <v>21.85</v>
       </c>
       <c r="F18">
-        <v>17485</v>
+        <v>16387.5</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="I18">
-        <v>170.75</v>
+        <v>22.45</v>
       </c>
       <c r="J18">
-        <v>17075</v>
+        <v>16837.5</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>-410</v>
+        <v>450</v>
       </c>
       <c r="M18">
-        <v>79.33</v>
+        <v>78.5</v>
       </c>
       <c r="N18">
-        <v>-489.33</v>
+        <v>371.5</v>
       </c>
       <c r="O18">
-        <v>410</v>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45904</v>
+      </c>
+      <c r="D19">
+        <v>500</v>
+      </c>
+      <c r="E19">
+        <v>43.65</v>
+      </c>
+      <c r="F19">
+        <v>21825</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>500</v>
+      </c>
+      <c r="I19">
+        <v>48.7</v>
+      </c>
+      <c r="J19">
+        <v>24350</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>2525</v>
+      </c>
+      <c r="M19">
+        <v>91.61</v>
+      </c>
+      <c r="N19">
+        <v>2433.39</v>
+      </c>
+      <c r="O19">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45904</v>
+      </c>
+      <c r="D20">
+        <v>2000</v>
+      </c>
+      <c r="E20">
+        <v>57.54</v>
+      </c>
+      <c r="F20">
+        <v>115075</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>2000</v>
+      </c>
+      <c r="I20">
+        <v>52.3</v>
+      </c>
+      <c r="J20">
+        <v>104600</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>-10475</v>
+      </c>
+      <c r="M20">
+        <v>318.22000000000003</v>
+      </c>
+      <c r="N20">
+        <v>-10793.22</v>
+      </c>
+      <c r="O20">
+        <v>10475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45904</v>
+      </c>
+      <c r="D21">
+        <v>325</v>
+      </c>
+      <c r="E21">
+        <v>63.45</v>
+      </c>
+      <c r="F21">
+        <v>20621.25</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>325</v>
+      </c>
+      <c r="I21">
+        <v>57.45</v>
+      </c>
+      <c r="J21">
+        <v>18671.25</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>-1950</v>
+      </c>
+      <c r="M21">
+        <v>83.01</v>
+      </c>
+      <c r="N21">
+        <v>-2033.01</v>
+      </c>
+      <c r="O21">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>167</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D22">
+        <v>150</v>
+      </c>
+      <c r="E22">
+        <v>145</v>
+      </c>
+      <c r="F22">
+        <v>21750</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22">
+        <v>150</v>
+      </c>
+      <c r="I22">
+        <v>129</v>
+      </c>
+      <c r="J22">
+        <v>19350</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>-2400</v>
+      </c>
+      <c r="M22">
+        <v>84.48</v>
+      </c>
+      <c r="N22">
+        <v>-2484.48</v>
+      </c>
+      <c r="O22">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>195</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D23">
+        <v>75</v>
+      </c>
+      <c r="E23">
+        <v>128.69999999999999</v>
+      </c>
+      <c r="F23">
+        <v>9652.5</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23">
+        <v>75</v>
+      </c>
+      <c r="I23">
+        <v>113.5</v>
+      </c>
+      <c r="J23">
+        <v>8512.5</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>-1140</v>
+      </c>
+      <c r="M23">
+        <v>63.64</v>
+      </c>
+      <c r="N23">
+        <v>-1203.6400000000001</v>
+      </c>
+      <c r="O23">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>169</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D24">
+        <v>300</v>
+      </c>
+      <c r="E24">
+        <v>169.05</v>
+      </c>
+      <c r="F24">
+        <v>50715</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>300</v>
+      </c>
+      <c r="I24">
+        <v>187</v>
+      </c>
+      <c r="J24">
+        <v>56100</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>5385</v>
+      </c>
+      <c r="M24">
+        <v>150.04</v>
+      </c>
+      <c r="N24">
+        <v>5234.96</v>
+      </c>
+      <c r="O24">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D25">
+        <v>200</v>
+      </c>
+      <c r="E25">
+        <v>115</v>
+      </c>
+      <c r="F25">
+        <v>23000</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25">
+        <v>200</v>
+      </c>
+      <c r="I25">
+        <v>122</v>
+      </c>
+      <c r="J25">
+        <v>24400</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1400</v>
+      </c>
+      <c r="M25">
+        <v>92.22</v>
+      </c>
+      <c r="N25">
+        <v>1307.78</v>
+      </c>
+      <c r="O25">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>99</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D26">
+        <v>350</v>
+      </c>
+      <c r="E26">
+        <v>152.88</v>
+      </c>
+      <c r="F26">
+        <v>53506.25</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26">
+        <v>350</v>
+      </c>
+      <c r="I26">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="J26">
+        <v>52570</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>-936.25</v>
+      </c>
+      <c r="M26">
+        <v>145.97999999999999</v>
+      </c>
+      <c r="N26">
+        <v>-1082.23</v>
+      </c>
+      <c r="O26">
+        <v>936.25</v>
       </c>
     </row>
   </sheetData>
